--- a/data/sentiment/AAII Sentiment.xlsx
+++ b/data/sentiment/AAII Sentiment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C309C47-D657-584F-890C-04F09DE1D7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C1D6EC-502A-8E41-BB36-17188ADEF0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10160" yWindow="3220" windowWidth="27240" windowHeight="16180" xr2:uid="{B930A3EF-683B-794B-B2E4-40886DCBD301}"/>
+    <workbookView xWindow="100" yWindow="2460" windowWidth="27240" windowHeight="16180" xr2:uid="{B930A3EF-683B-794B-B2E4-40886DCBD301}"/>
   </bookViews>
   <sheets>
     <sheet name="AAII" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -116,7 +116,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0913BF80-75CB-A349-8F9C-C38844F715A9}">
-  <dimension ref="A1:D2004"/>
+  <dimension ref="A1:D2005"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
@@ -28517,6 +28517,20 @@
       </c>
       <c r="D2004" s="3">
         <v>0.33203100000000002</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2005" s="1">
+        <v>46016</v>
+      </c>
+      <c r="B2005" s="3">
+        <v>0.374</v>
+      </c>
+      <c r="C2005" s="3">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="D2005" s="3">
+        <v>0.34799999999999998</v>
       </c>
     </row>
   </sheetData>
